--- a/output/Jiangxi/赣州市_news.xlsx
+++ b/output/Jiangxi/赣州市_news.xlsx
@@ -1368,7 +1368,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1379,13 +1379,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1853,28 +1846,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1883,126 +1879,124 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2442,9 +2436,7 @@
       <c r="M2">
         <v>0</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
+      <c r="N2"/>
       <c r="O2" t="s">
         <v>25</v>
       </c>
@@ -2492,9 +2484,7 @@
       <c r="M3">
         <v>0</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
+      <c r="N3"/>
       <c r="O3" t="s">
         <v>34</v>
       </c>
@@ -2542,9 +2532,7 @@
       <c r="M4">
         <v>0</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
+      <c r="N4"/>
       <c r="O4" t="s">
         <v>37</v>
       </c>
@@ -2592,9 +2580,7 @@
       <c r="M5">
         <v>0</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
+      <c r="N5"/>
       <c r="O5" t="s">
         <v>41</v>
       </c>
@@ -2642,9 +2628,7 @@
       <c r="M6">
         <v>0</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
+      <c r="N6"/>
       <c r="O6" t="s">
         <v>46</v>
       </c>
@@ -2692,9 +2676,7 @@
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
+      <c r="N7"/>
       <c r="O7" t="s">
         <v>48</v>
       </c>
@@ -2742,9 +2724,7 @@
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
+      <c r="N8"/>
       <c r="O8" t="s">
         <v>48</v>
       </c>
@@ -2792,9 +2772,7 @@
       <c r="M9">
         <v>0</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
+      <c r="N9"/>
       <c r="O9" t="s">
         <v>51</v>
       </c>
@@ -2842,9 +2820,7 @@
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
+      <c r="N10"/>
       <c r="O10" t="s">
         <v>53</v>
       </c>
@@ -2892,9 +2868,7 @@
       <c r="M11">
         <v>0</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
+      <c r="N11"/>
       <c r="O11" t="s">
         <v>59</v>
       </c>
@@ -2942,9 +2916,7 @@
       <c r="M12">
         <v>0</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
+      <c r="N12"/>
       <c r="O12" t="s">
         <v>62</v>
       </c>
@@ -2992,9 +2964,7 @@
       <c r="M13">
         <v>0</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
+      <c r="N13"/>
       <c r="O13" t="s">
         <v>66</v>
       </c>
@@ -3042,9 +3012,7 @@
       <c r="M14">
         <v>15</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
+      <c r="N14"/>
       <c r="O14" t="s">
         <v>70</v>
       </c>
@@ -3092,9 +3060,7 @@
       <c r="M15">
         <v>4</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
+      <c r="N15"/>
       <c r="O15" t="s">
         <v>74</v>
       </c>
@@ -3142,9 +3108,7 @@
       <c r="M16">
         <v>7</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
+      <c r="N16"/>
       <c r="O16" t="s">
         <v>78</v>
       </c>
@@ -3192,9 +3156,7 @@
       <c r="M17">
         <v>0</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
+      <c r="N17"/>
       <c r="O17" t="s">
         <v>81</v>
       </c>
@@ -3242,9 +3204,7 @@
       <c r="M18">
         <v>0</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
+      <c r="N18"/>
       <c r="O18" t="s">
         <v>83</v>
       </c>
@@ -3292,9 +3252,7 @@
       <c r="M19">
         <v>0</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
+      <c r="N19"/>
       <c r="O19" t="s">
         <v>85</v>
       </c>
@@ -3342,10 +3300,8 @@
       <c r="M20">
         <v>0</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="N20"/>
+      <c r="O20" s="2" t="s">
         <v>87</v>
       </c>
       <c r="P20" t="s">
@@ -3392,9 +3348,7 @@
       <c r="M21">
         <v>0</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
+      <c r="N21"/>
       <c r="O21" t="s">
         <v>89</v>
       </c>
@@ -3442,9 +3396,7 @@
       <c r="M22">
         <v>0</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
+      <c r="N22"/>
       <c r="O22" t="s">
         <v>92</v>
       </c>
@@ -3492,9 +3444,7 @@
       <c r="M23">
         <v>8</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
+      <c r="N23"/>
       <c r="O23" t="s">
         <v>96</v>
       </c>
@@ -3542,9 +3492,7 @@
       <c r="M24">
         <v>0</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
+      <c r="N24"/>
       <c r="O24" t="s">
         <v>99</v>
       </c>
@@ -3592,9 +3540,7 @@
       <c r="M25">
         <v>0</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
+      <c r="N25"/>
       <c r="O25" t="s">
         <v>102</v>
       </c>
@@ -3642,9 +3588,7 @@
       <c r="M26">
         <v>0</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
+      <c r="N26"/>
       <c r="O26" t="s">
         <v>105</v>
       </c>
@@ -3692,9 +3636,7 @@
       <c r="M27">
         <v>0</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
+      <c r="N27"/>
       <c r="O27" t="s">
         <v>107</v>
       </c>
@@ -3742,9 +3684,7 @@
       <c r="M28">
         <v>0</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
+      <c r="N28"/>
       <c r="O28" t="s">
         <v>109</v>
       </c>
@@ -3792,9 +3732,7 @@
       <c r="M29">
         <v>0</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
+      <c r="N29"/>
       <c r="O29" t="s">
         <v>112</v>
       </c>
@@ -3842,9 +3780,7 @@
       <c r="M30">
         <v>0</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
+      <c r="N30"/>
       <c r="O30" t="s">
         <v>114</v>
       </c>
@@ -3892,9 +3828,7 @@
       <c r="M31">
         <v>0</v>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
+      <c r="N31"/>
       <c r="O31" t="s">
         <v>118</v>
       </c>
@@ -3942,9 +3876,7 @@
       <c r="M32">
         <v>4</v>
       </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
+      <c r="N32"/>
       <c r="O32" t="s">
         <v>122</v>
       </c>
@@ -3992,9 +3924,7 @@
       <c r="M33">
         <v>34</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
+      <c r="N33"/>
       <c r="O33" t="s">
         <v>124</v>
       </c>
@@ -4042,9 +3972,7 @@
       <c r="M34">
         <v>14</v>
       </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
+      <c r="N34"/>
       <c r="O34" t="s">
         <v>126</v>
       </c>
@@ -4092,9 +4020,7 @@
       <c r="M35">
         <v>17</v>
       </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
+      <c r="N35"/>
       <c r="O35" t="s">
         <v>128</v>
       </c>
@@ -4142,9 +4068,7 @@
       <c r="M36">
         <v>16</v>
       </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
+      <c r="N36"/>
       <c r="O36" t="s">
         <v>130</v>
       </c>
@@ -4192,9 +4116,7 @@
       <c r="M37">
         <v>12</v>
       </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
+      <c r="N37"/>
       <c r="O37" t="s">
         <v>132</v>
       </c>
@@ -4242,9 +4164,7 @@
       <c r="M38">
         <v>12</v>
       </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
+      <c r="N38"/>
       <c r="O38" t="s">
         <v>134</v>
       </c>
@@ -4292,9 +4212,7 @@
       <c r="M39">
         <v>10</v>
       </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
+      <c r="N39"/>
       <c r="O39" t="s">
         <v>136</v>
       </c>
@@ -4342,9 +4260,7 @@
       <c r="M40">
         <v>8</v>
       </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
+      <c r="N40"/>
       <c r="O40" t="s">
         <v>138</v>
       </c>
@@ -4392,9 +4308,7 @@
       <c r="M41">
         <v>4</v>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
+      <c r="N41"/>
       <c r="O41" t="s">
         <v>141</v>
       </c>
@@ -4442,9 +4356,7 @@
       <c r="M42">
         <v>0</v>
       </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
+      <c r="N42"/>
       <c r="O42" t="s">
         <v>144</v>
       </c>
@@ -4492,9 +4404,7 @@
       <c r="M43">
         <v>24</v>
       </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
+      <c r="N43"/>
       <c r="O43" t="s">
         <v>148</v>
       </c>
@@ -4542,9 +4452,7 @@
       <c r="M44">
         <v>6</v>
       </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
+      <c r="N44"/>
       <c r="O44" t="s">
         <v>150</v>
       </c>
@@ -4592,9 +4500,7 @@
       <c r="M45">
         <v>13</v>
       </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
+      <c r="N45"/>
       <c r="O45" t="s">
         <v>153</v>
       </c>
@@ -4642,9 +4548,7 @@
       <c r="M46">
         <v>4</v>
       </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
+      <c r="N46"/>
       <c r="O46" t="s">
         <v>156</v>
       </c>
@@ -4692,9 +4596,7 @@
       <c r="M47">
         <v>0</v>
       </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
+      <c r="N47"/>
       <c r="O47" t="s">
         <v>158</v>
       </c>
@@ -4742,9 +4644,7 @@
       <c r="M48">
         <v>0</v>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
+      <c r="N48"/>
       <c r="O48" t="s">
         <v>160</v>
       </c>
@@ -4792,9 +4692,7 @@
       <c r="M49">
         <v>0</v>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
+      <c r="N49"/>
       <c r="O49" t="s">
         <v>162</v>
       </c>
@@ -4842,9 +4740,7 @@
       <c r="M50">
         <v>0</v>
       </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
+      <c r="N50"/>
       <c r="O50" t="s">
         <v>164</v>
       </c>
@@ -4892,9 +4788,7 @@
       <c r="M51">
         <v>0</v>
       </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
+      <c r="N51"/>
       <c r="O51" t="s">
         <v>166</v>
       </c>
@@ -4942,9 +4836,7 @@
       <c r="M52">
         <v>0</v>
       </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
+      <c r="N52"/>
       <c r="O52" t="s">
         <v>168</v>
       </c>
@@ -4992,9 +4884,7 @@
       <c r="M53">
         <v>0</v>
       </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
+      <c r="N53"/>
       <c r="O53" t="s">
         <v>172</v>
       </c>
@@ -5042,9 +4932,7 @@
       <c r="M54">
         <v>0</v>
       </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
+      <c r="N54"/>
       <c r="O54" t="s">
         <v>175</v>
       </c>
@@ -5092,9 +4980,7 @@
       <c r="M55">
         <v>0</v>
       </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
+      <c r="N55"/>
       <c r="O55" t="s">
         <v>178</v>
       </c>
@@ -5142,9 +5028,7 @@
       <c r="M56">
         <v>14</v>
       </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
+      <c r="N56"/>
       <c r="O56" t="s">
         <v>180</v>
       </c>
@@ -5192,9 +5076,7 @@
       <c r="M57">
         <v>12</v>
       </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
+      <c r="N57"/>
       <c r="O57" t="s">
         <v>183</v>
       </c>
@@ -5242,9 +5124,7 @@
       <c r="M58">
         <v>0</v>
       </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
+      <c r="N58"/>
       <c r="O58" t="s">
         <v>186</v>
       </c>
@@ -5292,9 +5172,7 @@
       <c r="M59">
         <v>0</v>
       </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
+      <c r="N59"/>
       <c r="O59" t="s">
         <v>188</v>
       </c>
@@ -5342,9 +5220,7 @@
       <c r="M60">
         <v>0</v>
       </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
+      <c r="N60"/>
       <c r="O60" t="s">
         <v>190</v>
       </c>
@@ -5392,9 +5268,7 @@
       <c r="M61">
         <v>0</v>
       </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
+      <c r="N61"/>
       <c r="O61" t="s">
         <v>192</v>
       </c>
@@ -5442,9 +5316,7 @@
       <c r="M62">
         <v>0</v>
       </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
+      <c r="N62"/>
       <c r="O62" t="s">
         <v>194</v>
       </c>
@@ -5492,9 +5364,7 @@
       <c r="M63">
         <v>0</v>
       </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
+      <c r="N63"/>
       <c r="O63" t="s">
         <v>196</v>
       </c>
@@ -5542,9 +5412,7 @@
       <c r="M64">
         <v>0</v>
       </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
+      <c r="N64"/>
       <c r="O64" t="s">
         <v>198</v>
       </c>
@@ -5592,9 +5460,7 @@
       <c r="M65">
         <v>0</v>
       </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
+      <c r="N65"/>
       <c r="O65" t="s">
         <v>203</v>
       </c>
@@ -5642,9 +5508,7 @@
       <c r="M66">
         <v>0</v>
       </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
+      <c r="N66"/>
       <c r="O66" t="s">
         <v>208</v>
       </c>
@@ -5692,9 +5556,7 @@
       <c r="M67">
         <v>0</v>
       </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
+      <c r="N67"/>
       <c r="O67" t="s">
         <v>212</v>
       </c>
@@ -5742,9 +5604,7 @@
       <c r="M68">
         <v>0</v>
       </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
+      <c r="N68"/>
       <c r="O68" t="s">
         <v>214</v>
       </c>
@@ -5792,9 +5652,7 @@
       <c r="M69">
         <v>0</v>
       </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
+      <c r="N69"/>
       <c r="O69" t="s">
         <v>219</v>
       </c>
@@ -5842,9 +5700,7 @@
       <c r="M70">
         <v>0</v>
       </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
+      <c r="N70"/>
       <c r="O70" t="s">
         <v>224</v>
       </c>
@@ -5892,9 +5748,7 @@
       <c r="M71">
         <v>0</v>
       </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
+      <c r="N71"/>
       <c r="O71" t="s">
         <v>227</v>
       </c>
@@ -5942,9 +5796,7 @@
       <c r="M72">
         <v>0</v>
       </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
+      <c r="N72"/>
       <c r="O72" t="s">
         <v>231</v>
       </c>
@@ -5992,9 +5844,7 @@
       <c r="M73">
         <v>0</v>
       </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
+      <c r="N73"/>
       <c r="O73" t="s">
         <v>233</v>
       </c>
@@ -6042,9 +5892,7 @@
       <c r="M74">
         <v>0</v>
       </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
+      <c r="N74"/>
       <c r="O74" t="s">
         <v>235</v>
       </c>
@@ -6092,9 +5940,7 @@
       <c r="M75">
         <v>0</v>
       </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
+      <c r="N75"/>
       <c r="O75" t="s">
         <v>238</v>
       </c>
@@ -6142,9 +5988,7 @@
       <c r="M76">
         <v>0</v>
       </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
+      <c r="N76"/>
       <c r="O76" t="s">
         <v>241</v>
       </c>
@@ -6192,9 +6036,7 @@
       <c r="M77">
         <v>0</v>
       </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
+      <c r="N77"/>
       <c r="O77" t="s">
         <v>244</v>
       </c>
@@ -6242,9 +6084,7 @@
       <c r="M78">
         <v>0</v>
       </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
+      <c r="N78"/>
       <c r="O78" t="s">
         <v>247</v>
       </c>
@@ -6292,9 +6132,7 @@
       <c r="M79">
         <v>0</v>
       </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
+      <c r="N79"/>
       <c r="O79" t="s">
         <v>250</v>
       </c>
@@ -6342,9 +6180,7 @@
       <c r="M80">
         <v>0</v>
       </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
+      <c r="N80"/>
       <c r="O80" t="s">
         <v>252</v>
       </c>
@@ -6392,9 +6228,7 @@
       <c r="M81">
         <v>0</v>
       </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
+      <c r="N81"/>
       <c r="O81" t="s">
         <v>254</v>
       </c>
@@ -6442,9 +6276,7 @@
       <c r="M82">
         <v>0</v>
       </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
+      <c r="N82"/>
       <c r="O82" t="s">
         <v>256</v>
       </c>
@@ -6492,9 +6324,7 @@
       <c r="M83">
         <v>0</v>
       </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
+      <c r="N83"/>
       <c r="O83" t="s">
         <v>259</v>
       </c>
@@ -6542,9 +6372,7 @@
       <c r="M84">
         <v>0</v>
       </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
+      <c r="N84"/>
       <c r="O84" t="s">
         <v>261</v>
       </c>
@@ -6592,9 +6420,7 @@
       <c r="M85">
         <v>0</v>
       </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
+      <c r="N85"/>
       <c r="O85" t="s">
         <v>265</v>
       </c>
@@ -6642,9 +6468,7 @@
       <c r="M86">
         <v>0</v>
       </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
+      <c r="N86"/>
       <c r="O86" t="s">
         <v>269</v>
       </c>
@@ -6692,9 +6516,7 @@
       <c r="M87">
         <v>0</v>
       </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
+      <c r="N87"/>
       <c r="O87" t="s">
         <v>272</v>
       </c>
@@ -6742,9 +6564,7 @@
       <c r="M88">
         <v>0</v>
       </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
+      <c r="N88"/>
       <c r="O88" t="s">
         <v>277</v>
       </c>
@@ -6792,9 +6612,7 @@
       <c r="M89">
         <v>0</v>
       </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
+      <c r="N89"/>
       <c r="O89" t="s">
         <v>280</v>
       </c>
@@ -6842,9 +6660,7 @@
       <c r="M90">
         <v>0</v>
       </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
+      <c r="N90"/>
       <c r="O90" t="s">
         <v>283</v>
       </c>
@@ -6892,9 +6708,7 @@
       <c r="M91">
         <v>0</v>
       </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
+      <c r="N91"/>
       <c r="O91" t="s">
         <v>288</v>
       </c>
@@ -6942,9 +6756,7 @@
       <c r="M92">
         <v>0</v>
       </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
+      <c r="N92"/>
       <c r="O92" t="s">
         <v>294</v>
       </c>
@@ -6992,9 +6804,7 @@
       <c r="M93">
         <v>0</v>
       </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
+      <c r="N93"/>
       <c r="O93" t="s">
         <v>298</v>
       </c>
@@ -7042,9 +6852,7 @@
       <c r="M94">
         <v>0</v>
       </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
+      <c r="N94"/>
       <c r="O94" t="s">
         <v>302</v>
       </c>
@@ -7092,9 +6900,7 @@
       <c r="M95">
         <v>0</v>
       </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
+      <c r="N95"/>
       <c r="O95" t="s">
         <v>305</v>
       </c>
@@ -7142,9 +6948,7 @@
       <c r="M96">
         <v>0</v>
       </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
+      <c r="N96"/>
       <c r="O96" t="s">
         <v>308</v>
       </c>
@@ -7192,9 +6996,7 @@
       <c r="M97">
         <v>0</v>
       </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
+      <c r="N97"/>
       <c r="O97" t="s">
         <v>311</v>
       </c>
@@ -7242,9 +7044,7 @@
       <c r="M98">
         <v>4</v>
       </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
+      <c r="N98"/>
       <c r="O98" t="s">
         <v>315</v>
       </c>
@@ -7292,9 +7092,7 @@
       <c r="M99">
         <v>0</v>
       </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
+      <c r="N99"/>
       <c r="O99" t="s">
         <v>319</v>
       </c>
@@ -7342,9 +7140,7 @@
       <c r="M100">
         <v>82</v>
       </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
+      <c r="N100"/>
       <c r="O100" t="s">
         <v>323</v>
       </c>
@@ -7392,9 +7188,7 @@
       <c r="M101">
         <v>131</v>
       </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
+      <c r="N101"/>
       <c r="O101" t="s">
         <v>326</v>
       </c>
@@ -7442,9 +7236,7 @@
       <c r="M102">
         <v>0</v>
       </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
+      <c r="N102"/>
       <c r="O102" t="s">
         <v>330</v>
       </c>
@@ -7492,9 +7284,7 @@
       <c r="M103">
         <v>0</v>
       </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
+      <c r="N103"/>
       <c r="O103" t="s">
         <v>332</v>
       </c>
@@ -7542,9 +7332,7 @@
       <c r="M104">
         <v>0</v>
       </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
+      <c r="N104"/>
       <c r="O104" t="s">
         <v>334</v>
       </c>
@@ -7592,9 +7380,7 @@
       <c r="M105">
         <v>0</v>
       </c>
-      <c r="N105">
-        <v>0</v>
-      </c>
+      <c r="N105"/>
       <c r="O105" t="s">
         <v>336</v>
       </c>
@@ -7642,9 +7428,7 @@
       <c r="M106">
         <v>0</v>
       </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
+      <c r="N106"/>
       <c r="O106" t="s">
         <v>339</v>
       </c>
@@ -7692,9 +7476,7 @@
       <c r="M107">
         <v>4</v>
       </c>
-      <c r="N107">
-        <v>0</v>
-      </c>
+      <c r="N107"/>
       <c r="O107" t="s">
         <v>343</v>
       </c>
@@ -7742,9 +7524,7 @@
       <c r="M108">
         <v>0</v>
       </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
+      <c r="N108"/>
       <c r="O108" t="s">
         <v>346</v>
       </c>
@@ -7792,9 +7572,7 @@
       <c r="M109">
         <v>4</v>
       </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
+      <c r="N109"/>
       <c r="O109" t="s">
         <v>349</v>
       </c>
@@ -7842,9 +7620,7 @@
       <c r="M110">
         <v>0</v>
       </c>
-      <c r="N110">
-        <v>0</v>
-      </c>
+      <c r="N110"/>
       <c r="O110" t="s">
         <v>353</v>
       </c>
@@ -7892,9 +7668,7 @@
       <c r="M111">
         <v>0</v>
       </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
+      <c r="N111"/>
       <c r="O111" t="s">
         <v>356</v>
       </c>
@@ -7942,9 +7716,7 @@
       <c r="M112">
         <v>4</v>
       </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
+      <c r="N112"/>
       <c r="O112" t="s">
         <v>359</v>
       </c>
@@ -7992,9 +7764,7 @@
       <c r="M113">
         <v>4</v>
       </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
+      <c r="N113"/>
       <c r="O113" t="s">
         <v>362</v>
       </c>
@@ -8042,9 +7812,7 @@
       <c r="M114">
         <v>4</v>
       </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
+      <c r="N114"/>
       <c r="O114" t="s">
         <v>364</v>
       </c>
@@ -8092,9 +7860,7 @@
       <c r="M115">
         <v>4</v>
       </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
+      <c r="N115"/>
       <c r="O115" t="s">
         <v>367</v>
       </c>
@@ -8142,9 +7908,7 @@
       <c r="M116">
         <v>5</v>
       </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
+      <c r="N116"/>
       <c r="O116" t="s">
         <v>369</v>
       </c>
@@ -8192,9 +7956,7 @@
       <c r="M117">
         <v>4</v>
       </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
+      <c r="N117"/>
       <c r="O117" t="s">
         <v>372</v>
       </c>
@@ -8242,9 +8004,7 @@
       <c r="M118">
         <v>4</v>
       </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
+      <c r="N118"/>
       <c r="O118" t="s">
         <v>374</v>
       </c>
@@ -8292,9 +8052,7 @@
       <c r="M119">
         <v>4</v>
       </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
+      <c r="N119"/>
       <c r="O119" t="s">
         <v>377</v>
       </c>
@@ -8342,9 +8100,7 @@
       <c r="M120">
         <v>0</v>
       </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
+      <c r="N120"/>
       <c r="O120" t="s">
         <v>381</v>
       </c>
@@ -8392,9 +8148,7 @@
       <c r="M121">
         <v>0</v>
       </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
+      <c r="N121"/>
       <c r="O121" t="s">
         <v>383</v>
       </c>
@@ -8442,9 +8196,7 @@
       <c r="M122">
         <v>0</v>
       </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
+      <c r="N122"/>
       <c r="O122" t="s">
         <v>387</v>
       </c>
@@ -8492,9 +8244,7 @@
       <c r="M123">
         <v>0</v>
       </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
+      <c r="N123"/>
       <c r="O123" t="s">
         <v>392</v>
       </c>
@@ -8542,9 +8292,7 @@
       <c r="M124">
         <v>0</v>
       </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
+      <c r="N124"/>
       <c r="O124" t="s">
         <v>395</v>
       </c>
@@ -8592,9 +8340,7 @@
       <c r="M125">
         <v>0</v>
       </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
+      <c r="N125"/>
       <c r="O125" t="s">
         <v>398</v>
       </c>
@@ -8642,9 +8388,7 @@
       <c r="M126">
         <v>0</v>
       </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
+      <c r="N126"/>
       <c r="O126" t="s">
         <v>401</v>
       </c>
@@ -8692,9 +8436,7 @@
       <c r="M127">
         <v>0</v>
       </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
+      <c r="N127"/>
       <c r="O127" t="s">
         <v>404</v>
       </c>
@@ -8742,9 +8484,7 @@
       <c r="M128">
         <v>0</v>
       </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
+      <c r="N128"/>
       <c r="O128" t="s">
         <v>407</v>
       </c>
@@ -8792,9 +8532,7 @@
       <c r="M129">
         <v>0</v>
       </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
+      <c r="N129"/>
       <c r="O129" t="s">
         <v>410</v>
       </c>
@@ -8842,9 +8580,7 @@
       <c r="M130">
         <v>0</v>
       </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
+      <c r="N130"/>
       <c r="O130" t="s">
         <v>412</v>
       </c>
@@ -8892,9 +8628,7 @@
       <c r="M131">
         <v>0</v>
       </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
+      <c r="N131"/>
       <c r="O131" t="s">
         <v>417</v>
       </c>
@@ -8942,9 +8676,7 @@
       <c r="M132">
         <v>0</v>
       </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
+      <c r="N132"/>
       <c r="O132" t="s">
         <v>420</v>
       </c>
@@ -8992,9 +8724,7 @@
       <c r="M133">
         <v>0</v>
       </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
+      <c r="N133"/>
       <c r="O133" t="s">
         <v>423</v>
       </c>
@@ -9042,9 +8772,7 @@
       <c r="M134">
         <v>0</v>
       </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
+      <c r="N134"/>
       <c r="O134" t="s">
         <v>426</v>
       </c>
@@ -9092,9 +8820,7 @@
       <c r="M135">
         <v>21</v>
       </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
+      <c r="N135"/>
       <c r="O135" t="s">
         <v>429</v>
       </c>
@@ -9142,9 +8868,7 @@
       <c r="M136">
         <v>0</v>
       </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
+      <c r="N136"/>
       <c r="O136" t="s">
         <v>432</v>
       </c>
@@ -9192,9 +8916,7 @@
       <c r="M137">
         <v>0</v>
       </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
+      <c r="N137"/>
       <c r="O137" t="s">
         <v>436</v>
       </c>
@@ -9242,9 +8964,7 @@
       <c r="M138">
         <v>0</v>
       </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
+      <c r="N138"/>
       <c r="O138" t="s">
         <v>439</v>
       </c>
@@ -9292,9 +9012,7 @@
       <c r="M139">
         <v>0</v>
       </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
+      <c r="N139"/>
       <c r="O139" t="s">
         <v>442</v>
       </c>
@@ -9303,6 +9021,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O20" r:id="rId1" display="http://zwkf.ganzhou.gov.cn/id_ff8080816c99a84f016ccb942ff1067d/open_directory_detail.shtml"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
